--- a/tools/importer/reports/import-supermoney-hero.report.xlsx
+++ b/tools/importer/reports/import-supermoney-hero.report.xlsx
@@ -49,7 +49,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-08-11T08:58:14.421Z</t>
+    <t>2026-08-11T10:35:49.471Z</t>
   </si>
   <si>
     <t>super.money RuPay Credit Card - UPI Cashback &amp; More | Kotak811</t>
